--- a/WorkBot/refactor-experimental/data/orders/Keck's Food Service/Keck's Food Service_Bakery_20251102.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Keck's Food Service/Keck's Food Service_Bakery_20251102.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,141 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>329.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>124440</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8 Grain</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>68.52</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>342.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>108900</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Seeds - Poppy</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>110.68</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>221.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>108970</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Garlic - Dry Minced</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>162.62</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>325.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>140660</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Coconut Swt Flake</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>61.43</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>61.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4100760</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Boston Coffee Cake - Apple Cinnamon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>55.80</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>55.80</t>
         </is>
       </c>
     </row>
